--- a/data/data_excluded.xlsx
+++ b/data/data_excluded.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,22 +459,42 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>vat_before</t>
+          <t>pedsql_totalself_before</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>vat_after</t>
+          <t>pedsql_totalself_after</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>pedsql_totalself_before</t>
+          <t>pedsql_santeself_after</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>pedsql_totalself_after</t>
+          <t>pedsql_emotionself_after</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pedsql_relationself_after</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pedsql_ecoleself_after</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pedsql_psycosocialself_after</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pedsql_physiqueself_after</t>
         </is>
       </c>
     </row>
@@ -504,13 +524,15 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>38.74224312653152</v>
+        <v>86.95652173913044</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>86.95652173913044</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -538,14 +560,28 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>39.95915493614461</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>76.08695652173913</v>
+      </c>
+      <c r="J3" t="n">
+        <v>70.65217391304348</v>
+      </c>
       <c r="K3" t="n">
-        <v>76.08695652173913</v>
+        <v>53.125</v>
       </c>
       <c r="L3" t="n">
-        <v>70.65217391304348</v>
+        <v>65</v>
+      </c>
+      <c r="M3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" t="n">
+        <v>80</v>
+      </c>
+      <c r="P3" t="n">
+        <v>53.125</v>
       </c>
     </row>
     <row r="4">
@@ -574,13 +610,15 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>32.16414908013607</v>
+        <v>75</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>75</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -608,14 +646,28 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>56.48039715580857</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>91.30434782608695</v>
+      </c>
+      <c r="J5" t="n">
+        <v>75</v>
+      </c>
       <c r="K5" t="n">
-        <v>91.30434782608695</v>
+        <v>78.125</v>
       </c>
       <c r="L5" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" t="n">
         <v>75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O5" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="P5" t="n">
+        <v>78.125</v>
       </c>
     </row>
     <row r="6">
@@ -644,13 +696,15 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>40.46344303566898</v>
+        <v>83.69565217391305</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>83.69565217391305</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -678,13 +732,15 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>38.62008136227815</v>
+        <v>46.73913043478261</v>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>46.73913043478261</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -712,13 +768,15 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>25.51845436139625</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>34.78260869565217</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -746,13 +804,15 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>21.59279657312702</v>
+        <v>46.73913043478261</v>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>46.73913043478261</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/data_excluded.xlsx
+++ b/data/data_excluded.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,40 +459,50 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>vat_before</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vat_after</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>pedsql_totalself_before</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pedsql_totalself_after</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pedsql_santeself_after</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>pedsql_emotionself_after</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>pedsql_relationself_after</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>pedsql_ecoleself_after</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>pedsql_psycosocialself_after</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>pedsql_physiqueself_after</t>
         </is>
@@ -524,15 +534,19 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
+        <v>38.74224312653152</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>86.95652173913044</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -560,27 +574,31 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>39.95915493614461</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>76.08695652173913</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>70.65217391304348</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>53.125</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>65</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>100</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>80</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -610,15 +628,19 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>32.16414908013607</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>75</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -646,27 +668,31 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
+        <v>56.48039715580857</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>91.30434782608695</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>75</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>78.125</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>65</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>75</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>80</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>73.33333333333333</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>78.125</v>
       </c>
     </row>
@@ -696,15 +722,19 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
+        <v>40.46344303566898</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>83.69565217391305</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -732,15 +762,19 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
+        <v>38.62008136227815</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>46.73913043478261</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -768,15 +802,19 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
+        <v>25.51845436139625</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>34.78260869565217</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -804,15 +842,19 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
+        <v>21.59279657312702</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
         <v>46.73913043478261</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/data_excluded.xlsx
+++ b/data/data_excluded.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,30 +479,60 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>pedsql_santeself_before</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>pedsql_santeself_after</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pedsql_emotionself_before</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>pedsql_emotionself_after</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pedsql_relationself_before</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>pedsql_relationself_after</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pedsql_ecoleself_before</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>pedsql_ecoleself_after</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pedsql_psycosocialself_before</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>pedsql_psycosocialself_after</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pedsql_physiqueself_before</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>pedsql_physiqueself_after</t>
         </is>
@@ -541,12 +571,30 @@
         <v>86.95652173913044</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>87.5</v>
+      </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>80</v>
+      </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>85</v>
+      </c>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>95</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -584,21 +632,39 @@
         <v>70.65217391304348</v>
       </c>
       <c r="M3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N3" t="n">
         <v>53.125</v>
-      </c>
-      <c r="N3" t="n">
-        <v>65</v>
       </c>
       <c r="O3" t="n">
         <v>75</v>
       </c>
       <c r="P3" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>75</v>
+      </c>
+      <c r="S3" t="n">
         <v>100</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="V3" t="n">
         <v>80</v>
       </c>
-      <c r="R3" t="n">
+      <c r="W3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X3" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -635,12 +701,30 @@
         <v>75</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>75</v>
+      </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>95</v>
+      </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>55</v>
+      </c>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>75</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>75</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -678,21 +762,39 @@
         <v>75</v>
       </c>
       <c r="M5" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="N5" t="n">
         <v>78.125</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>90</v>
+      </c>
+      <c r="P5" t="n">
         <v>65</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
+        <v>90</v>
+      </c>
+      <c r="R5" t="n">
         <v>75</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
+        <v>90</v>
+      </c>
+      <c r="T5" t="n">
         <v>80</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="U5" t="n">
+        <v>90</v>
+      </c>
+      <c r="V5" t="n">
         <v>73.33333333333333</v>
       </c>
-      <c r="R5" t="n">
+      <c r="W5" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="X5" t="n">
         <v>78.125</v>
       </c>
     </row>
@@ -729,12 +831,30 @@
         <v>83.69565217391305</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>84.375</v>
+      </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>80</v>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>90</v>
+      </c>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>80</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>84.375</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -769,12 +889,30 @@
         <v>46.73913043478261</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>65.625</v>
+      </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>40</v>
+      </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -809,12 +947,30 @@
         <v>34.78260869565217</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>37.5</v>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>35</v>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>35</v>
+      </c>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -849,12 +1005,30 @@
         <v>46.73913043478261</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>56.25</v>
+      </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>45</v>
+      </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
